--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -718,7 +718,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -812,7 +812,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -909,7 +909,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -971,7 +971,7 @@
     <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -995,7 +995,7 @@
     <t>薬剤の投与が予想される場所を記述するコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -1037,7 +1037,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1062,7 +1062,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1087,7 +1087,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1197,7 +1197,7 @@
     <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1209,7 +1209,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1237,7 +1237,7 @@
     <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1252,7 +1252,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1280,7 +1280,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1305,7 +1305,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1630,7 +1630,7 @@
     <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1910,7 +1910,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>単位時間あたりの用量</t>
@@ -1971,7 +1971,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
